--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_84_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_84_R9.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7814</v>
+        <v>3.5523</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0083</v>
+        <v>3.6111</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2268</v>
+        <v>-0.0588</v>
       </c>
       <c r="G2" t="n">
         <v>0.0605</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.293</v>
+        <v>0.0639</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3031</v>
+        <v>-0.094</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0101</v>
+        <v>0.1579</v>
       </c>
       <c r="V2" t="n">
         <v>2.9641</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9091</v>
+        <v>2.5742</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5923</v>
+        <v>3.4926</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6832</v>
+        <v>-0.9184</v>
       </c>
       <c r="G3" t="n">
         <v>-6.3511</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4229</v>
+        <v>-0.7578</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.7924</v>
+        <v>-0.892</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3695</v>
+        <v>0.1342</v>
       </c>
       <c r="V3" t="n">
         <v>7.3636</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. DANGUBIC</t>
+          <t>S. SANLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1825</v>
+        <v>-0.3415</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5381</v>
+        <v>-1.527</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7206</v>
+        <v>1.1855</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.156</v>
+        <v>0.3328</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.384</v>
+        <v>-1.4272</v>
       </c>
       <c r="I4" t="n">
-        <v>1.228</v>
+        <v>1.76</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0132</v>
+        <v>-0.1669</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1646</v>
+        <v>-0.6687</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1778</v>
+        <v>0.5018</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1692</v>
+        <v>0.4997</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2195</v>
+        <v>-0.7584</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0502</v>
+        <v>1.2582</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1359</v>
+        <v>-0.6743</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4732</v>
+        <v>-0.2003</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3374</v>
+        <v>-0.474</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.4665</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SANLI</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.761</v>
+        <v>-0.7806</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1481</v>
+        <v>-0.2105</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3871</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3328</v>
+        <v>-0.896</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4272</v>
+        <v>-0.3707</v>
       </c>
       <c r="I5" t="n">
-        <v>1.76</v>
+        <v>-0.5253</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1669</v>
+        <v>0.0877</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6687</v>
+        <v>0.9243</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5018</v>
+        <v>-0.8366</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4997</v>
+        <v>-0.9837</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7584</v>
+        <v>-1.2949</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2582</v>
+        <v>0.3113</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0939</v>
+        <v>-0.5779</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8215</v>
+        <v>-0.44</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2724</v>
+        <v>-0.1379</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>N. DANGUBIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.048</v>
+        <v>-1.4396</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4778</v>
+        <v>0.0794</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-1.5189</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.896</v>
+        <v>-0.156</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3707</v>
+        <v>-1.384</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5253</v>
+        <v>1.228</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0877</v>
+        <v>1.0132</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9243</v>
+        <v>-0.1646</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8366</v>
+        <v>1.1778</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9837</v>
+        <v>-1.1692</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2949</v>
+        <v>-1.2195</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3113</v>
+        <v>0.0502</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8452</v>
+        <v>0.8788</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7073</v>
+        <v>1.0146</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1379</v>
+        <v>-0.1357</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9304</v>
+        <v>-1.4665</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4754</v>
+        <v>-1.518</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9453</v>
+        <v>3.1379</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.4207</v>
+        <v>-4.6559</v>
       </c>
       <c r="G7" t="n">
         <v>0.4812</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1163</v>
+        <v>-1.1589</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8962</v>
+        <v>-0.7035</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2201</v>
+        <v>-0.4553</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3939</v>
+        <v>-3.1176</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1275</v>
+        <v>1.2022</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.5214</v>
+        <v>-4.3198</v>
       </c>
       <c r="G8" t="n">
         <v>-1.248</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7721</v>
+        <v>-1.4958</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7073</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0649</v>
+        <v>-0.8632</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1532</v>
+        <v>-3.7754</v>
       </c>
       <c r="E9" t="n">
-        <v>0.724</v>
+        <v>1.0346</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.8772</v>
+        <v>-4.81</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5071</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6614</v>
+        <v>-1.2836</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8962</v>
+        <v>-0.5856</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7653</v>
+        <v>-0.698</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9138</v>
+        <v>-4.6443</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8544</v>
+        <v>-0.6185</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0593</v>
+        <v>-4.0257</v>
       </c>
       <c r="G10" t="n">
         <v>-4.6914</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0627</v>
+        <v>-0.7932</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3159</v>
+        <v>-0.2822</v>
       </c>
       <c r="V10" t="n">
         <v>1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.2373</v>
+        <v>-9.490500000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>9.4552</v>
+        <v>10.2018</v>
       </c>
       <c r="F11" t="n">
-        <v>-19.6922</v>
+        <v>-19.6921</v>
       </c>
       <c r="G11" t="n">
         <v>-13.9751</v>
@@ -1285,7 +1285,7 @@
         <v>-10.5064</v>
       </c>
       <c r="J11" t="n">
-        <v>6.2043</v>
+        <v>6.204300000000001</v>
       </c>
       <c r="K11" t="n">
         <v>5.904</v>
@@ -1303,7 +1303,7 @@
         <v>-10.8065</v>
       </c>
       <c r="P11" t="n">
-        <v>4.639</v>
+        <v>4.638999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-6.958799999999999</v>
@@ -1312,13 +1312,13 @@
         <v>11.5977</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.5456</v>
+        <v>-5.798799999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.7914</v>
+        <v>-3.0443</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.7545</v>
+        <v>-2.7542</v>
       </c>
       <c r="V11" t="n">
         <v>5.644600000000001</v>
@@ -1327,7 +1327,7 @@
         <v>14.0007</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.356200000000001</v>
+        <v>-8.356199999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.917400000000001</v>
+        <v>8.479900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>9.6357</v>
+        <v>9.399800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7183</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>3.3019</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0278</v>
+        <v>1.5903</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8496</v>
+        <v>0.6137</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1782</v>
+        <v>0.9766</v>
       </c>
       <c r="V12" t="n">
         <v>2.428</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.041</v>
+        <v>4.0854</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4195</v>
+        <v>2.3632</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6214</v>
+        <v>1.7222</v>
       </c>
       <c r="G13" t="n">
         <v>5.3894</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3536</v>
+        <v>0.6908</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0455</v>
+        <v>-0.1019</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6919</v>
+        <v>0.7927</v>
       </c>
       <c r="V13" t="n">
         <v>0.7886</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5035</v>
+        <v>2.059</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8952</v>
+        <v>1.2491</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6083</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.5954</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0009</v>
+        <v>0.5564</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.051</v>
+        <v>0.3029</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0518</v>
+        <v>0.2535</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7886</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3207</v>
+        <v>1.0176</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8558</v>
+        <v>4.6199</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.535</v>
+        <v>-3.6023</v>
       </c>
       <c r="G15" t="n">
         <v>2.1131</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9577</v>
+        <v>0.6546</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3383</v>
+        <v>0.1024</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6194</v>
+        <v>0.5522</v>
       </c>
       <c r="V15" t="n">
         <v>-1.7501</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.989</v>
+        <v>0.3592</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1903</v>
+        <v>-0.0234</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2012</v>
+        <v>0.3826</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06909999999999999</v>
+        <v>3.8694</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2521</v>
+        <v>1.6577</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3212</v>
+        <v>2.2117</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5698</v>
+        <v>2.951</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1918</v>
+        <v>1.4186</v>
       </c>
       <c r="L16" t="n">
-        <v>0.378</v>
+        <v>1.5324</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5007</v>
+        <v>0.9184</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4439</v>
+        <v>0.2391</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0568</v>
+        <v>0.6793</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>-3.7112</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2989</v>
+        <v>0.0413</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7106</v>
+        <v>0.2008</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5881999999999999</v>
+        <v>-0.1595</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.5387</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>G. PALATIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3935</v>
+        <v>0.1573</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2125</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1809</v>
+        <v>0.1573</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8694</v>
+        <v>0.1573</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6577</v>
+        <v>0.1573</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2117</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.951</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4186</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5324</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9184</v>
+        <v>0.1573</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2391</v>
+        <v>0.1573</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6793</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.0154</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.7112</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0756</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4367</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3611</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>B. TIMOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2581</v>
+        <v>0.1573</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1918</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9337</v>
+        <v>0.1573</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7381</v>
+        <v>0.1573</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6348</v>
+        <v>0.1573</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8968</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4535</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2892</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1643</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1916</v>
+        <v>0.1573</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.924</v>
+        <v>0.1573</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2676</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9962</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8259</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1703</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. PALATIN</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1573</v>
+        <v>0.079</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.2466</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1573</v>
+        <v>-1.1676</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1573</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1573</v>
+        <v>-0.2521</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.3212</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.5698</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.1918</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1573</v>
+        <v>-0.5007</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>-0.4439</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.0568</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.3888</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.767</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.6218</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.5387</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. TIMOR</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1573</v>
+        <v>-0.366</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1.2295</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1573</v>
+        <v>-1.5955</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1573</v>
+        <v>0.6601</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1573</v>
+        <v>-0.6015</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1.2615</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.3611</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.8465</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1573</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1573</v>
+        <v>-1.1161</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.1828</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.0927</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4975</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9379</v>
+        <v>-0.6335</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9936</v>
+        <v>1.838</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9315</v>
+        <v>-2.4714</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6601</v>
+        <v>-0.7381</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6015</v>
+        <v>-1.6348</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2615</v>
+        <v>0.8968</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3611</v>
+        <v>1.4535</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.2892</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8465</v>
+        <v>1.1643</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-2.1916</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1161</v>
+        <v>-1.924</v>
       </c>
       <c r="O21" t="n">
-        <v>0.415</v>
+        <v>-0.2676</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3892</v>
+        <v>1.1046</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0395</v>
+        <v>0.472</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4288</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6468</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4975</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5626</v>
+        <v>-5.1581</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7022</v>
+        <v>-2.2304</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8605</v>
+        <v>-2.9277</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5996</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.3361</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3497</v>
+        <v>0.1221</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2812</v>
+        <v>0.2139</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3584</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.2373</v>
+        <v>10.2371</v>
       </c>
       <c r="E23" t="n">
-        <v>19.6922</v>
+        <v>19.6923</v>
       </c>
       <c r="F23" t="n">
         <v>-9.455</v>
@@ -2224,16 +2224,16 @@
         <v>20.1793</v>
       </c>
       <c r="K23" t="n">
-        <v>9.3728</v>
+        <v>9.372799999999998</v>
       </c>
       <c r="L23" t="n">
         <v>10.8067</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.2042</v>
+        <v>-6.204199999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.9038</v>
+        <v>-5.903799999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-0.3003000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>6.9588</v>
       </c>
       <c r="S23" t="n">
-        <v>6.545800000000001</v>
+        <v>6.5457</v>
       </c>
       <c r="T23" t="n">
         <v>2.7544</v>
       </c>
       <c r="U23" t="n">
-        <v>3.7911</v>
+        <v>3.791100000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-5.644600000000001</v>
